--- a/xls/square_un_16_tri3_17_0.xlsx
+++ b/xls/square_un_16_tri3_17_0.xlsx
@@ -461,34 +461,34 @@
         <v>11</v>
       </c>
       <c r="B16">
-        <v>380</v>
+        <v>340</v>
       </c>
       <c r="C16" t="s">
         <v>11</v>
       </c>
       <c r="D16">
-        <v>340</v>
+        <v>297</v>
       </c>
       <c r="E16" t="s">
         <v>12</v>
       </c>
       <c r="F16">
-        <v>340</v>
+        <v>297</v>
       </c>
       <c r="G16" t="s">
         <v>13</v>
       </c>
       <c r="H16">
-        <v>1842</v>
+        <v>1596</v>
       </c>
       <c r="I16">
-        <v>-2.309112578361784</v>
+        <v>-2.2036968143812214</v>
       </c>
       <c r="J16">
-        <v>-1.9786148712132967</v>
+        <v>-2.001888359272205</v>
       </c>
       <c r="K16">
-        <v>-0.8168205708815162</v>
+        <v>-0.9628057374099025</v>
       </c>
     </row>
   </sheetData>

--- a/xls/square_un_16_tri3_17_0.xlsx
+++ b/xls/square_un_16_tri3_17_0.xlsx
@@ -482,13 +482,13 @@
         <v>1596</v>
       </c>
       <c r="I16">
-        <v>-2.2036968143812214</v>
+        <v>-2.2022963788061527</v>
       </c>
       <c r="J16">
-        <v>-2.001888359272205</v>
+        <v>-2.0011711840169726</v>
       </c>
       <c r="K16">
-        <v>-0.9628057374099025</v>
+        <v>-0.9625485482471937</v>
       </c>
     </row>
   </sheetData>
